--- a/output/Scrape_DrogaRaia_2025-08-15.xlsx
+++ b/output/Scrape_DrogaRaia_2025-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D206"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,4100 +453,3380 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7896013563594</t>
+          <t>7898917294765</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Creme de Cabelo Tratamento Novex Óleo de Argan 400g</t>
+          <t>Bebida de Arroz Kids Rice Milk Sem Lactose 500g Unilife</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13.99</v>
+        <v>54.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/novex-creme-de-tratamento-oleo-de-argan-400g.html</t>
+          <t>https://www.drogaraia.com.br/bebida-de-arroz-kids-rice-milk-sem-lactose-500g-unilife-923072.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>803397</t>
+          <t>733698</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shampoo Sirius Restaurador Intenso Ação Anti-Frizz 1L</t>
+          <t>Proteína Vegetal em Pó Essential Nutrition Veggie Protein Cacau 455g</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>167.7</v>
+        <v>264.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-profissional-restaurador-intenso-de-sirius-1l-803397.html</t>
+          <t>https://www.drogaraia.com.br/veggie-essential-nutrition-lata-450g-todos-os-sabores-envio-rapido-733698.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8005610531663</t>
+          <t>7908609503249</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shampoo Wella Oil Reflections Nutrição 250ml</t>
+          <t xml:space="preserve">Kit Vitamina B6 Piridoxina Unilife 5 unidades 60 cápsulas </t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>137.99</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-wella-oil-reflections-250ml-860174.html</t>
+          <t>https://www.drogaraia.com.br/kit-5-vitamina-b6-piridoxina-60-capsulas-unilife-680555.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1003756</t>
+          <t>7891142982087</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tesoura para Unhas Dos Pés Em Aço Inoxidável Qvs</t>
+          <t>Mantecorp Epidrat Calm Hidratante Facial Restaurador 120Ml</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.95</v>
+        <v>152.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tesoura-para-unhas-dos-pes-em-aco-inoxidavel-qvs-039-1003756.html</t>
+          <t>https://www.drogaraia.com.br/mantecorp-epidrat-calm-hidratante-facial-restaurador-120ml-676038.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7891317014414</t>
+          <t>3605532612690</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citta Bromidrato de Citalopram 20mg 30 comprimidos</t>
+          <t>La Vie Est Belle Lancôme Eau De Parfum 30ml - Perfume Feminino</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92.48999999999999</v>
+        <v>309.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/citta-20mg.html</t>
+          <t>https://www.drogaraia.com.br/la-vie-est-belle-lancome-woman-eau-de-parfum-30ml-856084.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>7899360243669</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kit Truss Equilibrium Mask Frizz Zero (4 Produtos)</t>
+          <t>LIPGLOSS MáGICO PINK 21 FANCY DOLLY 01 7ML</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>599.99</v>
+        <v>13.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-truss-equilibrium-mask-frizz-zero-4-produtos-774700.html</t>
+          <t>https://www.drogaraia.com.br/lipgloss-magico-pink-21-fancy-dolly-01-7ml-970170.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7898625791549</t>
+          <t>692701</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECONSTRUTOR TRUSS USO OBRIGATóRIO PLUS 260ML</t>
+          <t>ELIZABETH ARDEN KIT RED DOOR FEMININO (EAU DE TOILETTE 30ML + LOÇÃO CORPORAL 50ML + GEL DE BANHO 50ML)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>196.49</v>
+        <v>221.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/reconstrutor-truss-uso-obrigatorio-plus-260ml-919972.html</t>
+          <t>https://www.drogaraia.com.br/elizabeth-arden-kit-red-door-feminino-eau-de-toilette-30ml-locao-corporal-50ml-gel-de-banho-50ml-692701.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7896033203371</t>
+          <t>7898493367952</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHUPETA BICO DE SILICONE FUNNY 6M+ AZUL - LILLO</t>
+          <t>CINTA TêNIS ELBOW PRETO CHA751 - CHANTAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/chupeta-bico-de-silicone-funny-6m-azul-lillo-715339.html</t>
+          <t>https://www.drogaraia.com.br/cinta-tenis-elbow-preto-cha751-chantal-874985.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7898576399733</t>
+          <t>980371</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUGADOR ROSA - FLUTUA ROSE</t>
+          <t>Shampoo Wella Professionals Invigo Nutri-Enrich Nutrição 1000ml</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>297.35</v>
+        <v>164.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/sugador-rosa-flutua-rose-982202.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-nutri-enrich-wella-volumetria-1000ml-980371.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7899525658130</t>
+          <t>6018132980740</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kit Colher Buba Baby Colorido com 6 unidades</t>
+          <t>Shampoo Bio Extratus Umectante Óleo de Coco 1L</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.9</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/buba-kit-colheres-colorido-3-unidades.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-bio-extratus-umectante-oleo-de-coco-1litro-966058.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>606529424350</t>
+          <t>5708932731997</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TRUE WHEY PROTEIN CONCENTRATE ZERO LACTOSE 900G TRUE SOURCE Baunilha</t>
+          <t>CURATIVO HIDROCOLóIDE COM ALGINATO CONTORNO 6X8CM - COMFEEL PLUS - COLOPLAST 33280</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>232.43</v>
+        <v>30.08</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/true-whey-protein-concentrate-zero-lactose-900g-true-source-baunilha-927686.html</t>
+          <t>https://www.drogaraia.com.br/curativo-hidrocoloide-com-alginato-contorno-6x8cm-comfeel-plus-coloplast-33280-746910.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7898680413424</t>
+          <t>3474637089702</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TREONATO MAGNéSIO E TREONINA 60 CáPSULAS BIOKLEIN</t>
+          <t>Redken Acidic Bonding Concentrate - Condicionador 1L</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>376.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/treonato-magnesio-e-treonina-60-capsulas-bioklein-811773.html</t>
+          <t>https://www.drogaraia.com.br/redken-acidic-bonding-concentrate-condicionador-1000ml-676293.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7898616750494</t>
+          <t>7290011521653</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCAA 10:1:1 (250G) - SABOR: MORANGO</t>
+          <t>Óleo Capilar Moroccanoil Treatment Light 25ml</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>89.90000000000001</v>
+        <v>147.17</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/bcaa-10-1-1-250g-sabor-morango-882643.html</t>
+          <t>https://www.drogaraia.com.br/moroccanoil-treatment-light-oleo-capilar-25ml-694140.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7899852024226</t>
+          <t>7908609504581</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLUSH VULT FUN BRONZE NATURAL 6,5G</t>
+          <t>Kit Complexo B Unilife 5 unidades 60 cápsulas</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34.45</v>
+        <v>63.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/blush-vult-fun-bronze-natural-6-5g-947233.html</t>
+          <t>https://www.drogaraia.com.br/kit-5-complexo-b-60-capsulas-unilife-730447.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7896331705720</t>
+          <t>7897129304248</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Resfenol 10 cápsulas</t>
+          <t>Theraskin Klaviê Clinical Loção Hidratante 190ml</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.9</v>
+        <v>92.17</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/resfenol-anti-gripal-10-capsulas.html</t>
+          <t>https://www.drogaraia.com.br/theraskin-klavie-clinical-locao-hidratante-190ml-644491.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7896181907497</t>
+          <t>1013178431278</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotar Anlodipino 2,5mg + Losartana Potássica 50mg 30 cápsulas</t>
+          <t>Kit L'Oréal Professionnel Serie Expert Pro Longer - Shampoo 300ml + Máscara 250g</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>71.59</v>
+        <v>303.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/lotar-2-5-50mg-30-capsulas.html</t>
+          <t>https://www.drogaraia.com.br/kit-l-oreal-professionnel-serie-expert-pro-longer-shampoo-e-mascara-250g-687557.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>883894</t>
+          <t>986525</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOSS BOTTLED EAU DE PARFUM MASCULINO 100ML</t>
+          <t>CONDICIONADOR ELSEVE HYDRA DETOX ANTICASPA 400ML</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>409.9</v>
+        <v>127.99</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/boss-bottled-eau-de-parfum-masculino-100ml-883894.html</t>
+          <t>https://www.drogaraia.com.br/condicionador-elseve-hydra-detox-anticaspa-400ml-986525.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3607342107977</t>
+          <t>7890000060165</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PERFUME CALVIN KLEIN ETERNITY AQUA MASCULINO 100 ML</t>
+          <t>MáSCARA PVC P/REANIMADOR C/GARRA CRISTAL NR 1 INFANTIL - UND</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>463.48</v>
+        <v>47.81</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-calvin-klein-eternity-aqua-masculino-100-ml-980936.html</t>
+          <t>https://www.drogaraia.com.br/mascara-pvc-p-reanimador-c-garra-cristal-nr-1-infantil-und-714652.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>949566</t>
+          <t>3401399373237</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Energético em Pó Essential Nutrition Carbolifit Palationese 300g</t>
+          <t>Gel de Banho Bioderma Atoderm Hidratante 200ml</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>111.51</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/carbolift-essential-nutrition-300g-949566.html</t>
+          <t>https://www.drogaraia.com.br/atoderm-gel-douche-200ml-927006.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7896046700676</t>
+          <t>7898924603949</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POMADA PARA CABELO MASCULINA FIXAçãO NORMAL EFEITO MATTE CHARMING MEN 50G</t>
+          <t>Shampoo Haskell Bananeira Nutrição 300ml</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.9</v>
+        <v>63.57</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/pomada-para-cabelo-masculina-fixacao-normal-efeito-matte-charming-men-50g-1016527.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-haskell-bananeira-300ml-945802.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7891033475971</t>
+          <t>7908885328598</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Desodorante Antitranspirante Aerosol Eudora Instance Frutas Vermelhas Feminino 48H 150Ml</t>
+          <t>GEL CERA FIXADOR YELSEW SUPER CERA 240G - KIT C/ 3UN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19.19</v>
+        <v>39.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/eudora-instance-frutas-vermelhas-desodorante-aerosol-150ml-642716.html</t>
+          <t>https://www.drogaraia.com.br/gel-cera-fixador-yelsew-super-cera-240g-kit-c-3un-1024027.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7898322343324</t>
+          <t>7898949409731</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KIT SILVER LINE SHAMPOO MENTOLADO 300ML + SHAVING GEL 200ML + HIDRATANTE PóS BARBA 140ML</t>
+          <t>Shampoo Antiqueda Fortalecedor 415Ml  Tío Nacho</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>103.49</v>
+        <v>41.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-silver-line-shampoo-mentolado-300ml-shaving-gel-200ml-hidratante-pos-barba-140ml-938149.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-antiqueda-fortalecedor-415ml-tio-nacho-1000950.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3326240005474</t>
+          <t>5060173370718</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ulric De Varens So Varens Paris Eau De Parfum 75Ml - Avarias Na Embalagem</t>
+          <t>Tangle teezer the ultimate escova para finalizar preta</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>131.35</v>
+        <v>161.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/ulric-de-varens-so-varens-paris-eau-de-parfum-75ml-avarias-na-embalagem-693866.html</t>
+          <t>https://www.drogaraia.com.br/tangle-teezer-the-ultimate-escova-para-finalizar-preta-673375.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>692651</t>
+          <t>7899026493094</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOMMY HILFIGER TOMMY GIRL FEMININO EAU DE TOILETTE 100ML</t>
+          <t>LA ROCHE-POSAY LIPIKAR LOçãO 400ML</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>513.33</v>
+        <v>278.24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tommy-hilfiger-tommy-girl-feminino-eau-de-toilette-100ml-692651.html</t>
+          <t>https://www.drogaraia.com.br/la-roche-posay-lipikar-locao-400ml-929306.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7899662602560</t>
+          <t>987872</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Condicionador Nick Vick Defesa Diária Proteção UV 250ml</t>
+          <t>KIT CHEF WHEY 907G + COLLAGEN 300GR + COQUETELEIRA 700ML - CHEF WHEY + CREATINA 600GR - INOVATIVE NUTRIENTS Morango</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47.9</v>
+        <v>479.99</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/condicionador-defesa-diaria-nick-vick-alta-performance-250ml-717442.html</t>
+          <t>https://www.drogaraia.com.br/kit-chef-whey-907g-collagen-300gr-coqueteleira-700ml-chef-whey-creatina-600gr-inovative-nutrients-morango-987872.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8436097093571</t>
+          <t>7891548800947</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BYPHASSE FLEUR DE TIARé DE TAHITI - GEL DE BANHO 500ML</t>
+          <t>KIT COM 3 GLICO 500MG 60 CáPSULAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56</v>
+        <v>239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/byphasse-fleur-de-tiare-de-tahiti-gel-de-banho-500ml-898675.html</t>
+          <t>https://www.drogaraia.com.br/kit-com-3-glico-500mg-60-capsulas-818180.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7899706197502</t>
+          <t>7891317026066</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CREME PARA PENTEAR LEAVE IN ELSEVE CACHOS SONHOS 250ML</t>
+          <t>Vitamina D3 Colecalciferol 7.000UI 4 cápsulas</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.27</v>
+        <v>15.59</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/creme-para-pentear-leave-in-elseve-cachos-sonhos-250ml-740216.html</t>
+          <t>https://www.drogaraia.com.br/eurofarma-vitamina-d3-7-000ui-4-capsulas.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7898692980914</t>
+          <t>7891066000973</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABSOLUTE NEW YORK MAGIQUICK MAGIC UNHAS POSTIçAS MéDIA AUTOCOLANTE QUADRADA BLACK 24 UNIDADES</t>
+          <t>Refil Massageador Orbital Lixa para Pés Needs 2 Unidades</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>43.9</v>
+        <v>11.99</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/absolute-new-york-magiquick-magic-unhas-posticas-media-autocolante-quadrada-black-24-unidades-676903.html</t>
+          <t>https://www.drogaraia.com.br/needs-refil-para-massageador-pes.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>815231</t>
+          <t>6291108735503</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ÔMEGA 3 EPA DHA 1G (120 CAPS) VITAFOR - PADRãO: ÚNICO</t>
+          <t>Collection Exclusif Tabac Maison Alhambra Eau De Parfum 100ml - Perfume Masculino</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>149.9</v>
+        <v>156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/omega-3-epa-dha-1g-120-caps-vitafor-padrao-unico-815231.html</t>
+          <t>https://www.drogaraia.com.br/maison-alhambra-collection-exclusif-tabac-eau-de-parfum-perfume-masculino-100ml-933681.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>834685</t>
+          <t>7898629561445</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desodorante Antitranspirante Aerosol Adidas Sport Energy Masculino 72h Cool &amp; Dry 150ml </t>
+          <t>TOP WHEY 3W + PERFORMANCE POTE 900G MORANGO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18.07</v>
+        <v>199.48</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/desodorante-aerossol-adidas-masculino-sport-energy-150ml-834685.html</t>
+          <t>https://www.drogaraia.com.br/top-whey-3w-performance-pote-900g-morango-985661.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>748370</t>
+          <t>7908083526550</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Royal Marina Diamond Princess Marina de Bourbon Eau de Parfum 100ml - Perfume Feminino</t>
+          <t>ESMALTE GEL NATI JANAíNA RODRIGUES MINHAS RAINHAS ME ACHANDO 8G</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>384</v>
+        <v>30.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/marina-de-bourbon-royal-marina-eau-de-parfum-perfume-feminino-748370.html</t>
+          <t>https://www.drogaraia.com.br/esmalte-gel-nati-janaina-rodrigues-minhas-rainhas-me-achando-8g-970205.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8058664134472</t>
+          <t>666472</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COPO DE TREINAMENTO 6M+ CHICCO VERDE</t>
+          <t>KIT ESCOVA ELéTRICA SONICPRO 50 + REFIL SONICPRO BRANQUEADORA COM 2 UNIDADES</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>79.90000000000001</v>
+        <v>829.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/copo-de-treinamento-6m-chicco-verde-872930.html</t>
+          <t>https://www.drogaraia.com.br/kit-escova-eletrica-sonicpro-50-refil-sonicpro-branqueadora-com-2-unidades-666472.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7792253844687</t>
+          <t>748927050967</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kit Braé Feminino Deo Parfum 100ml + Leave-In Finalizador para Cabelo Hair Repair 260ml</t>
+          <t>100% WHEY PROTEIN GOLD STANDARD (2,270KG) NOVO RÓTULO - SABOR: MORANGO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>294.99</v>
+        <v>899.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-brae-for-her-deo-parfum-e-essential-hair-repair-spray-2-produtos-1007144.html</t>
+          <t>https://www.drogaraia.com.br/100-whey-protein-gold-standard-2-270kg-novo-rotulo-sabor-morango-882823.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7896094208537</t>
+          <t>7897517918187</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LIBBS FILTRUM ULTRA SECO PELE OLEOSA FPS30 60G</t>
+          <t>Tesoura de Cabelo Vertix Tesoura Iniciante Laser 65 cm - 1 unidade</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>103.57</v>
+        <v>94.98</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/libbs-filtrum-ultra-seco-pele-oleosa-fps30-60g-687355.html</t>
+          <t>https://www.drogaraia.com.br/vertix-tesoura-iniciante-laser-6-5-1-unidade.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7908458306879</t>
+          <t>7898623950047</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SALON LINE, MáSCARA CAPILAR, MARIA NATUREZA, NUTRIçãO EXTRAORDINáRIA, MURUMURU E ABACATE, VEGANA - TODOS OS TIPOS DE CABELOS, 200 G</t>
+          <t>Gelatina Capilar Salon Line #Todecacho Mix 550G</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15.9</v>
+        <v>33.67</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/salon-line-mascara-capilar-maria-natureza-nutricao-extraordinaria-murumuru-e-abacate-vegana-todos-os-tipos-de-cabelos-200-g-862355.html</t>
+          <t>https://www.drogaraia.com.br/gelatina-capilar-salon-line-todecacho-mix-550g-654165.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7896509974217</t>
+          <t>7898583668068</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gel Líquido Cabelo Cacheado Soul Power Modeling Curls Seiva Modeladora 315 ml</t>
+          <t>COLáGENO HIDROLISADO - 300G ABACAXI COM GENGIBRE - FTW</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27.29</v>
+        <v>150.38</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/soul-power-gel-liquido-modeling-curls-315ml.html</t>
+          <t>https://www.drogaraia.com.br/colageno-hidrolisado-300g-abacaxi-com-gengibre-ftw-727960.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7891142144270</t>
+          <t>78950000603</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PROTETOR SOLAR FACIAL EPISOL COLOR FPS30 PELE CLARA 40G</t>
+          <t>Kit Wella Professionals Invigo Nutri-Enrich - Shampoo 1L (2 produtos)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>92.5</v>
+        <v>248.9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/protetor-solar-facial-episol-color-fps30-pele-clara-40g-879144.html</t>
+          <t>https://www.drogaraia.com.br/kit-wella-professionals-invigo-nutri-enrich-shampoo-1000ml-2-unidades-926835.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7792252963754</t>
+          <t>887230</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KIT JACQUES JANINE HAIR SUN PROTECT SHAMPOO CONDICIONADOR E MáSCARA P (3 PRODUTOS)</t>
+          <t>Biogens kit 4x maca peruana 1000mg 180 tabletes vegan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>126.99</v>
+        <v>284.25</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-jacques-janine-hair-sun-protect-shampoo-condicionador-e-mascara-p-3-produtos-927918.html</t>
+          <t>https://www.drogaraia.com.br/biogens-kit-4x-maca-peruana-1000mg-180-tabletes-vegan-887230.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>987930</t>
+          <t>948798</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xtreme Gainer c/ Creatina 3Kg - Bio Sports USA Sabor:Baunilha</t>
+          <t>CERA DEPILATóRIA DEPIL BELLA CAMOMILA 250G</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>142</v>
+        <v>23.78</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/xtreme-gainer-3kg-bio-sports-usa-baunilha-987930.html</t>
+          <t>https://www.drogaraia.com.br/cera-depilatoria-depil-bella-camomila-250g-948798.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3386460028424</t>
+          <t>1009980271</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Femme Individualle Montblanc Eau de Toilette 75ml - Perfume Feminino</t>
+          <t>Kit Capilar Revlon Professional Uniq One All In One - Shampoo 490 ml + Máscara 300 ml</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>438.79</v>
+        <v>370.9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-montblanc-individuelle-feminino-edt-75-ml-865669.html</t>
+          <t>https://www.drogaraia.com.br/kit-capilar-revlon-professional-uniq-one-all-in-one-shampoo-490-ml-mascara-300-ml-795344.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>871561</t>
+          <t>854094</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shampoo Braé Soul Color Proteção da Cor 250ml</t>
+          <t>SHAVING NERK EMBAIXADOR CREME PRé E PóS BARBA + PERFUME SPICE 500ml</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49.99</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-brae-soul-color-250ml-871561.html</t>
+          <t>https://www.drogaraia.com.br/shaving-nerk-embaixador-creme-pre-e-pos-barba-perfume-spice-500ml-854094.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7896770982140</t>
+          <t>7908236800667</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Roupa Íntima Tena Pants Confort G/EG 32 unidades</t>
+          <t>Frontal Alprazolam 1mg 30 comprimidos</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>129.9</v>
+        <v>128</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/roupa-intima-tena-pants-confort-g-eg-32-unidades-666477.html</t>
+          <t>https://www.drogaraia.com.br/frontal-1-mg-30-comprimidos-b1.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7891033925506</t>
+          <t>7793481205653</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shampoo Eudora Siáge Reconstrói Os Fios 4D 250ml</t>
+          <t>KIT 03 COLáGENOS HIDROLISADO VERISOL LATA 250G MAXINUTRI</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>44.9</v>
+        <v>213.03</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/eudora-siage-reconstroi-os-fios-4d-shampoo-250ml-676993.html</t>
+          <t>https://www.drogaraia.com.br/kit-03-colagenos-hidrolisado-verisol-lata-250g-maxinutri-875353.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7897517928506</t>
+          <t>7899760800790</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shampoo A Seco Ricca Menta 150Ml 2850</t>
+          <t>L´Arrëe After Color Shampoo Cabelos Coloridos C/Mecha 1Litro</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.75</v>
+        <v>132.77</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-a-seco-ricca-menta-150ml-2850-646800.html</t>
+          <t>https://www.drogaraia.com.br/l-039arree-after-color-shampoo-cabelos-coloridos-c-mecha-1litro-971861.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7893244127830</t>
+          <t>7898512720386</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3X GEL BT NITRATO DOBRO SABOR REDBERRY 10 UNIDADES 30G</t>
+          <t>ISOTONIC POUCH 1KG - MARACUJÁ</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>479.9</v>
+        <v>42.14</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/3x-gel-bt-nitrato-dobro-sabor-redberry-10-unidades-30g-998954.html</t>
+          <t>https://www.drogaraia.com.br/isotonic-pouch-1kg-maracuja-1011307.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8003085701260</t>
+          <t>7896714212081</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA FLORENTINA LAVENDER LIQUID SOAP 500ML</t>
+          <t>Prednisona 5mg 20 comprimidos Neo Química Genérico</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46.47</v>
+        <v>19.59</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/la-florentina-lavender-liquid-soap-500ml-1016641.html</t>
+          <t>https://www.drogaraia.com.br/prednisona-neoquimica-genericos-5mg-com-20comprimidos.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1000043596330</t>
+          <t>7898415010010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KIT ENGOV AFTER 4 SABORES - 2 UNIDADES CADA</t>
+          <t>CALCANHEIRA SILIGEL PARA ESPORãO CALCâNEO TAM P - PAR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>100</v>
+        <v>84.88</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-engov-after-4-sabores-2-unidades-cada-690645.html</t>
+          <t>https://www.drogaraia.com.br/calcanheira-siligel-para-esporao-calcaneo-tam-p-par-720236.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8411061930878</t>
+          <t>7896032689879</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Seduction In Black Banderas Eau De Toilette - Perfume Masculino 200ml</t>
+          <t>TRACTA MATTE 12H CORRETIVO LíQUIDO MATTE 11 ESCURO 7G</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>299</v>
+        <v>36.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/antonio-bandeiras-black-seduction-200ml-704338.html</t>
+          <t>https://www.drogaraia.com.br/tracta-matte-12h-corretivo-liquido-matte-11-escuro-7g-837798.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8022297065014</t>
+          <t>7500435172721</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alfaparf Semi Di Lino Diamond Extraordinary All In One - Protetor Térmico 125Ml</t>
+          <t>Kit Lenço Umedecido Pampers Higiene Completa 48 unidades 4 pacotes</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>109.9</v>
+        <v>36</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/alfaparf-milano-professional-semi-di-lino-diamond-extraordinary-all-in-one-leave-in-125ml-688510.html</t>
+          <t>https://www.drogaraia.com.br/pampers-kit-lencos-umedecidos-higiene-completa-leve-4-pague-3-com-48-unidades-cada.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7898943477606</t>
+          <t>3351500011469</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ÁGUA OXIGENADA ACQUAFLORA 10 VOLUMES 120ML</t>
+          <t>Azzaro Pour Homme Eau de Toilette 200ml - Perfume Masculino</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20.15</v>
+        <v>729</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/agua-oxigenada-acquaflora-10-volumes-120ml-640445.html</t>
+          <t>https://www.drogaraia.com.br/azzaro-pour-homme-edt-200ml-2020-703917.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>250000000033</t>
+          <t>7896015568214</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PROTESE MAMARIA EM SILICONE TRIANGULAR 1052 ORTHOPAUHER 7AO 10 8</t>
+          <t>Clavulin Bd Amoxicilina Tri-hidratada 400mg + Clavulanato de Potássio 57mg Suspensão 70ml</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>251</v>
+        <v>54.61</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/protese-mamaria-em-silicone-triangular-1052-orthopauher-7ao-10-8-935122.html</t>
+          <t>https://www.drogaraia.com.br/clavulin-bd-400mg-70ml.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>730109</t>
+          <t>7896094202276</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Metilfolato L Metil Folato Ácido Fólico 60 Capsulas Biogens Neutro</t>
+          <t>Cebrilin Cloridrato de Paroxetina 30mg 30 comprimidos</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>39.9</v>
+        <v>226.98</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/metilfolato-l-metil-folato-acido-folico-60-capsulas-biogens-730109.html</t>
+          <t>https://www.drogaraia.com.br/cebrilin-30mg-30-comprimidos-c1.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7897153000420</t>
+          <t>993834</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kit Leite Condensado Flormel Zero Açúcar 200G com 2 Unidades </t>
+          <t>CONDICIONADOR DE CABELO HASKELL CAVALO FORTE 300ML</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53.8</v>
+        <v>44.9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-leite-condensado-flormel-zero-acucar-200g-com-2-unidades-u-unica-1000434.html</t>
+          <t>https://www.drogaraia.com.br/condicionador-de-cabelo-haskell-cavalo-forte-300ml-993834.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>974736</t>
+          <t>682363</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gucci Flora Gorgeous Jasmine Eau de Parfum 50ml - Perfume Feminino</t>
+          <t>Kit Isdin - Sérum Facial E Protetor Solar Facial Com Cor Fps 50 Escura</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>799</v>
+        <v>306.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/gucci-flora-gourgeous-jasmine-edp-perfume-feminino-50ml-974736.html</t>
+          <t>https://www.drogaraia.com.br/kit-isdin-serum-facial-e-protetor-solar-facial-com-cor-fps-50-escura-682363.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7898567894612</t>
+          <t>7898662061872</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MáSCARA PROGRESSIVA NO CHUVEIRO INTENSIVE ABELHA RAINHA 300G</t>
+          <t>HASTES FLEXíVEIS MINNá MAQUIAGEM C/75UN</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38.99</v>
+        <v>1.29</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/mascara-progressiva-no-chuveiro-intensive-abelha-rainha-300g-881644.html</t>
+          <t>https://www.drogaraia.com.br/hastes-flexiveis-minna-maquiagem-c-75un-654276.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7896015529086</t>
+          <t>8435415011341</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Anoro Ellipta Brometo de Umeclidinio 62,5mcg + Trifenatato de Vilanterol 25mcg 30 doses</t>
+          <t>Classique Jean Paul Gaultier Eau De Toilette 100ml - Perfume Feminino</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>367.02</v>
+        <v>652.9</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/anoro-62-5-25-mcg-30-doses.html</t>
+          <t>https://www.drogaraia.com.br/jean-paul-gaultier-classique-edt-perfume-feminino-100ml-973743.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7899732112159</t>
+          <t>7908885321513</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ATLAS CREATINA (90G) - PADRãO: ÚNICO</t>
+          <t>SHAMPOO OURIBEL 1000ML DETOX - KIT C/2UN</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>50.96</v>
+        <v>39.9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/atlas-creatina-90g-padrao-unico-1011874.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-ouribel-1000ml-detox-kit-c-2un-1019005.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>789500000238</t>
+          <t>7896111972038</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KIT FACIAL VICHY MINéRAL 89 - SéRUM 50ML E SéRUM PARA OS OLHOS 15ML</t>
+          <t>SPRAY SECANTE DE ESMALTE IMPALA MELALEUCA 400ML</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>361.9</v>
+        <v>39.99</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-facial-vichy-mineral-89-serum-50ml-e-serum-para-os-olhos-15ml-796183.html</t>
+          <t>https://www.drogaraia.com.br/spray-secante-de-esmalte-impala-melaleuca-400ml-1014237.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7899572813384</t>
+          <t>713441</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Máscara de Cabelo Fortificante Lola Cosmetics Rapunzel 450g</t>
+          <t>CLINICMAIS CHá MORANGO 10 SACHêS 15G - CHá MAIS</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>39.9</v>
+        <v>13.86</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/lola-cosmetics-rapunzel-mascara-fortificante-450g-764707.html</t>
+          <t>https://www.drogaraia.com.br/clinicmais-cha-morango-10-saches-15g-cha-mais-713441.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4015630066841</t>
+          <t>7899592812671</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tiras-teste de Glicemia Accu-Chek Guide 50 unidades</t>
+          <t>CHá SUBLIME INVERNO 10 SACHêS - CHá MAIS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>134.99</v>
+        <v>6.5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/accu-chek-guide-com-50-tiras.html</t>
+          <t>https://www.drogaraia.com.br/cha-sublime-inverno-10-saches-cha-mais-721367.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7908607305111</t>
+          <t>7898576391027</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANDAGEM ELáSTICA ADESIVA KINESIOLóGICA DELLAMED MARROM</t>
+          <t>Pincel Chanfrado para Blush Océane Pink My Apple OCN5 com 1 Unidade</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>35.91</v>
+        <v>25.19</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/bandagem-elastica-adesiva-kinesiologica-dellamed-marrom-980925.html</t>
+          <t>https://www.drogaraia.com.br/oceane-pincel-chanfrado-para-blush.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7896311771783</t>
+          <t>815191</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MAGNéSIO 60 Cápsulas Neutro</t>
+          <t>SIMFORT (PROBIóTICO) 10 SACHêS 2G - VITAFOR</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51.83</v>
+        <v>51.9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/magnesio-60-capsulas-neutro-828897.html</t>
+          <t>https://www.drogaraia.com.br/simfort-probiotico-10-saches-2g-vitafor-815191.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7899026408340</t>
+          <t>7899083122173</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ESMALTE COLORAMA CREMOSO GABRIELE 8ML</t>
+          <t>ESMALTE TOP BEAUTY CREMOSO PREMIUM NEON CRAZY FIRE BALL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>18.99</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/esmalte-colorama-cremoso-gabriele-8ml-1014356.html</t>
+          <t>https://www.drogaraia.com.br/esmalte-top-beauty-cremoso-premium-neon-crazy-fire-ball-944163.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7899572811052</t>
+          <t>853884</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shampoo Camomila Lola Brilho Intenso 250ml</t>
+          <t>PENTE PROFISSIONAL SHORT WICKS MECHAS QUIFF DIMIL 20CM</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>57.99</v>
+        <v>7.9</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-lola-camomila-250ml-986288.html</t>
+          <t>https://www.drogaraia.com.br/pente-profissional-short-wicks-mechas-quiff-dimil-20cm-853884.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7891000073100</t>
+          <t>7895750913273</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cereal Infantil Nestlé Mucilon Arroz e Aveia Integral 600g</t>
+          <t>KIT WHEY 100% PURE 907G BAUNILHA + DECA TESTONA COM 60</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>27.99</v>
+        <v>239.9</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/mucilon-cereal-infantil-arroz-e-aveia-600g.html</t>
+          <t>https://www.drogaraia.com.br/kit-whey-100-pure-907g-baunilha-deca-testona-com-60-632333.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7893339006842</t>
+          <t>7795076201323</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2X BLISTER GUMMIES CABELOS, PELE E UNHAS- GLOBAL- 42 GOMAS</t>
+          <t>KIT ARVENSIS CACHOS CRESPO E CRESPíSSIMOS + GELEIA ALTA 250G</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>109.25</v>
+        <v>289.7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/2x-blister-gummies-cabelos-pele-e-unhas-global-42-gomas-936447.html</t>
+          <t>https://www.drogaraia.com.br/kit-arvensis-cachos-crespo-e-crespissimos-geleia-alta-250g-992812.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7899706206532</t>
+          <t>7898902621620</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kit SkinCeuticals Sérum 10 Antioxidante 15ml + Sérum Corretor Phyto Corrective 15ml</t>
+          <t>ENVOLUCRON GEL - ATIVIDADE CEREBRAL NúCLEO QUâNTICO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>413</v>
+        <v>99</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/skinceuticals-kit-serum-antioxidante-serum-10-15ml-phyto-corrective-15ml.html</t>
+          <t>https://www.drogaraia.com.br/envolucron-gel-atividade-cerebral-nucleo-quantico-814476.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7891182001892</t>
+          <t>6015045338388</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Esmalte Cremoso Risqué 8ml - Paris</t>
+          <t>KIT 2 COLáGENO DERMUP VERISOL + VITAMINAS 90 CáPSULAS MAXINUTRI</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6.19</v>
+        <v>117.8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/risque-esmalte-cremoso-paris-8ml.html</t>
+          <t>https://www.drogaraia.com.br/kit-2-colageno-dermup-verisol-vitaminas-90-capsulas-maxinutri-999034.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7896523208404</t>
+          <t>7898952577564</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nevralgex Dipirona Monoidratada 300mg + Cafeína 50 mg + Citrato de Orfenadrina 35 mg 30 comprimidos</t>
+          <t>FOREVER LISS CACHOS MÁSCARA 250G</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>26.09</v>
+        <v>34.9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/nevralgex-30-comprimidos.html</t>
+          <t>https://www.drogaraia.com.br/forever-liss-cachos-mascara-250g-886290.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7898606743901</t>
+          <t>7500435197014</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SéRUM LEAVE-IN CADIVEU PROFESSIONAL SOS HAIR REMEDY 15 IN 1 - 120ML</t>
+          <t>Máscara Hidratante Pantene Colágeno Hidrata E Resgata 550Ml</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>68.98999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/serum-leave-in-cadiveu-professional-sos-hair-remedy-15-in-1-120ml-899570.html</t>
+          <t>https://www.drogaraia.com.br/mascara-hidratante-pantene-colageno-hidrata-e-resgata-550ml-665945.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7898474841624</t>
+          <t>7891548804440</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICIONADOR TOK BOTHâNICO PERA 400ML</t>
+          <t>COMPRE 2 LEVE 3 SELêNIO 500MG 60 CáPSULAS</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17.54</v>
+        <v>181.7</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-shampoo-condicionador-tok-bothanico-pera-400ml-943699.html</t>
+          <t>https://www.drogaraia.com.br/compre-2-leve-3-selenio-500mg-60-capsulas-829684.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7896032654976</t>
+          <t>7896026171397</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bruna Tavares BT Glue - Fixador de Glitter 10ml</t>
+          <t>Hidratante Corporal Fisiogel Loção Cremosa Pele Seca e Sensível com 100ml</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>46</v>
+        <v>48.19</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/bruna-tavares-bt-glue-fixador-de-glitter-10ml-734892.html</t>
+          <t>https://www.drogaraia.com.br/fisiogel-locao-cremosa-100ml.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7893595771041</t>
+          <t>5901832068655</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kit com 2 Floral Thérapi Serenide  Muwiz</t>
+          <t>Mr Sharp La Rive Eau de Toilette 100ml - Perfume Masculino</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>85.90000000000001</v>
+        <v>289.9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-com-2-floral-therapi-serenide-muwiz-1001193.html</t>
+          <t>https://www.drogaraia.com.br/perfume-la-rive-mr-sharp-edt-masculino-100ml-980804.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>769856</t>
+          <t>7898687781090</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SHAMPOO NUTRITIVO ELA é CARIOCA LOLA COSMETICS 500ML</t>
+          <t>CONDICIONADOR BEAUTY SOLUTION LOKENZZI 320ML FORTALECIMENTO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>44.9</v>
+        <v>47.99</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-nutritivo-ela-e-carioca-lola-cosmetics-500ml-769856.html</t>
+          <t>https://www.drogaraia.com.br/condicionador-beauty-solution-lokenzzi-320ml-fortalecimento-1007919.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7891000255544</t>
+          <t>7908609502594</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Composto Lácteo Nestonutri 800G</t>
+          <t>KIT 5 ÓLEO DE COCO EXTRA VIRGEM 60 CáPSULAS UNILIFE</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>74.98</v>
+        <v>121.9</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/composto-lacteo-nestonutri-800g-703646.html</t>
+          <t>https://www.drogaraia.com.br/kit-5-oleo-de-coco-extra-virgem-60-capsulas-unilife-680540.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7896467567292</t>
+          <t>7890000082532</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kit Condicionador 200ml E Oil Reflections 30ml Light - Wella</t>
+          <t>CAMARA DE AR PARA CADEIRA FREEDOM - ARO 20</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>183.99</v>
+        <v>19.12</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-condicionador-200ml-e-oil-reflections-30ml-light-wella-871226.html</t>
+          <t>https://www.drogaraia.com.br/camara-de-ar-para-cadeira-freedom-aro-20-717980.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>693277</t>
+          <t>7896048605993</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CALVIN KLEIN EUPHORIA FEMININO EAU DE PARFUM 100ML</t>
+          <t>Protetor Solar Corporal FPS 30 Needs Solar Spray Aerossol 200ml</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>523.45</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/calvin-klein-euphoria-feminino-eau-de-parfum-100ml-693277.html</t>
+          <t>https://www.drogaraia.com.br/needs-protetor-solar-aerossol-fps30-200ml.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7500435127240</t>
+          <t>7897169221567</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Absorvente Always Suave P com Abas 8 unidades</t>
+          <t>PINCEL DE PELO MISTO COM CABO DE MADEIRA PARA BARBA Bege</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5.25</v>
+        <v>10.9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/always-absorvente-super-proteo-suave-com-abas-8-unidades.html</t>
+          <t>https://www.drogaraia.com.br/pincel-de-pelo-misto-com-cabo-de-madeira-para-barba-bege-875986.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7898524347687</t>
+          <t>7898593050976</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MáSCARA DE HIDRATAçãO SALON LINE SOS BOMBA VITAMINAS 1KG</t>
+          <t>COLáGENO HIDROLISADO 2 EM 1 VERISOL + Q10 (30 SACHêS DE 5G) - SABOR: UVA VERDE</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.99</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/mascara-de-hidratacao-salon-line-sos-bomba-vitaminas-1kg-831982.html</t>
+          <t>https://www.drogaraia.com.br/colageno-hidrolisado-2-em-1-verisol-q10-30-saches-de-5g-sabor-uva-verde-1015207.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>871113</t>
+          <t>7899621106030</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kit Enrich Shampoo, Condicionador, Máscara E Oil Reflections - Wella</t>
+          <t>BEST WHEY SACHê (DISPLAY COM 15 SACHêS - 35G) - SABOR: DOUBLE CHOCOLATE (SACHê 40G)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>330.99</v>
+        <v>210.9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-enrich-shampoo-condicionador-mascara-e-oil-reflections-wella-871113.html</t>
+          <t>https://www.drogaraia.com.br/best-whey-sache-display-com-15-saches-35g-sabor-double-chocolate-sache-40g-1009695.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8011003818112</t>
+          <t>48675991063</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Versace Crystal Absolut Edp Perfume Feminino 90Ml</t>
+          <t>Brincos studex supermaxxi</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>659.9</v>
+        <v>32.59</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/versace-crystal-absolut-edp-perfume-feminino-90ml-769853.html</t>
+          <t>https://www.drogaraia.com.br/brincos-studex-supermaxxi-895575.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7805092518074</t>
+          <t>4260198090634</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Combo Siàge Pro Cronology: Shampoo 250Ml + Condicionador 200Ml + Escova De Desembaraçar</t>
+          <t>LáPIS DE SOBRANCELHAS VEGANO GENTLE BROWN BENECOS 6G</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>155.97</v>
+        <v>145.88</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/combo-siage-pro-cronology-shampoo-250ml-condicionador-200ml-escova-de-desembaracar-931221.html</t>
+          <t>https://www.drogaraia.com.br/lapis-de-sobrancelhas-vegano-gentle-brown-benecos-6g-925545.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3614226404084</t>
+          <t>920313</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ÓLEO CAPILAR WELLA PROFESSIONALS REFLECTION 100ML</t>
+          <t>PRINCIPIA TôNICO SKINCARE 7% ÁCIDO LáTICO + 1% ÁCIDO SALICíLICO AL-7 COM 120ML</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>262.47</v>
+        <v>83.25</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/oleo-capilar-wella-professionals-reflection-100ml-944134.html</t>
+          <t>https://www.drogaraia.com.br/principia-tonico-skincare-7-acido-latico-1-acido-salicilico-al-7-com-120ml-920313.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7908414444195</t>
+          <t>3614273069540</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TERMôMETRO TOUCH CARE DIGITAL MULTI SAúDE HC498</t>
+          <t>Yves Saint Laurent Libre Intense Eau De Parfum - Perfume Feminino 50ml</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>84.65000000000001</v>
+        <v>716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/termometro-touch-care-digital-multi-saude-hc498-1006195.html</t>
+          <t>https://www.drogaraia.com.br/yves-saint-laurent-libre-intense-eau-de-parfum-perfume-feminino-50ml-852575.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7896196702032</t>
+          <t>9001616691133</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEL CRIOTERáPICO REDUTOR DE MEDIDAS CELULITE E ESTRIAS MENTOL CANFORA E CAFEíNA 750G</t>
+          <t>Kit 2 Chupetas Coleção Fundo Do Mar 0-6 Meses Rosa  - Mam</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>56.9</v>
+        <v>61.9</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/gel-crioterapico-redutor-de-medidas-celulite-e-estrias-mentol-canfora-e-cafeina-750g-888085.html</t>
+          <t>https://www.drogaraia.com.br/kit-2-chupetas-colecao-fundo-do-mar-0-6-meses-rosa-mam-717000.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7896615101019</t>
+          <t>3454090001978</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Copo Descartável para Inalador Soniclear 15 unidades</t>
+          <t>PARIS ELYSEES MAX MASCULINO EAU DE TOILETTE 100ML</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>29.14</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/copinho-descartavel-para-inalador-soniclear-666646.html</t>
+          <t>https://www.drogaraia.com.br/paris-elysees-max-masculino-eau-de-toilette-100ml-692776.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5060420231038</t>
+          <t>719346065399</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bomba de Tirar Leite Elétrica Lansinoh  Single Compact</t>
+          <t>PERFUME BRITNEY SPEARS FANTASY EAU DE PARFUM FEMININO 100ML</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>399.9</v>
+        <v>165.9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/bomba-tira-leite-eletrica-single-compact-lansinoh-900570.html</t>
+          <t>https://www.drogaraia.com.br/perfume-britney-spears-fantasy-eau-de-parfum-feminino-100ml-1021397.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7898610370087</t>
+          <t>7898586020894</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shampoo Haskell Cavalo Forte 500Ml</t>
+          <t>ENERGY PRO GEL - 15 SACHêS DE 30G BANANA COM AçAí - SUDRACT NUTRITION</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>84.88</v>
+        <v>78.61</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/shampoo-haskell-cavalo-forte-500ml-636079.html</t>
+          <t>https://www.drogaraia.com.br/energy-pro-gel-15-saches-de-30g-banana-com-acai-sudract-nutrition-731762.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7898698361472</t>
+          <t>7898687734713</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Femme Buckingham Parfum 25ml - Perfume Feminino</t>
+          <t>Café Proteico Equaliv Body Coffee Protein Vanilla 375g</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>79.98999999999999</v>
+        <v>176.72</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-femme-buckingham-25ml-656566.html</t>
+          <t>https://www.drogaraia.com.br/equaliv-body-coffee-vanilla-375g.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7891317025205</t>
+          <t>7891010253790</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dixil Minoxidil 50mg/ml Solução Spray Capilar 50ml</t>
+          <t>Hidratante Facial Neutrogena Face Care Intensive Antissinais FPS 22 100g</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>59.39</v>
+        <v>44.9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/dixil-50mg-ml-solucao-spray-50ml.html</t>
+          <t>https://www.drogaraia.com.br/hidratante-facial-neutrogena-face-care-intensive-antissinais-fps-22-100g-667883.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7898955705049</t>
+          <t>7898487860124</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Leite vegetal original a tal da castanha 1l</t>
+          <t>SONDA ASPIRAçãO TRAQUEAL MEDSONDA (08) - 100 UNIDADES</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>27.88</v>
+        <v>108</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/leite-vegetal-original-a-tal-da-castanha-1l-620379.html</t>
+          <t>https://www.drogaraia.com.br/sonda-aspiracao-traqueal-medsonda-08-100-unidades-925495.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7896086910974</t>
+          <t>7794147142763</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HIDRATANTE CORPORAL AMêNDOAS MAHOGANY 350ML</t>
+          <t>KIT ARVENSIS CACHOS NATURAIS ONDULADOS SHAMPOO ATIV MASCARA</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>59.5</v>
+        <v>172.11</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/hidratante-corporal-amendoas-mahogany-350ml-923079.html</t>
+          <t>https://www.drogaraia.com.br/kit-arvensis-cachos-naturais-ondulados-shampoo-ativ-mascara-1007596.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>980579</t>
+          <t>7908825797736</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PERFUME CHANEL ALLURE HOMME SPORT 100 ML</t>
+          <t>COLORAçAO HASKELL TON 834 LOURO CLR DOUR ACOBREADO-KIT C/3UN</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1476.08</v>
+        <v>139.9</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-chanel-allure-homme-sport-100-ml-980579.html</t>
+          <t>https://www.drogaraia.com.br/coloracao-haskell-ton-834-louro-clr-dour-acobreado-kit-c-3un-1005449.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1192119</t>
+          <t>7898741801344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KIT 10UN EQUIPO DE NUTRIçãO ENTERAL 2 VIAS FRESENIUS</t>
+          <t>CíLIOS POSTIçOS KISS NY IMPRESS PRESS-ON FALSIES REFIL 02</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>22.14</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-10un-equipo-de-nutricao-enteral-2-vias-fresenius-982586.html</t>
+          <t>https://www.drogaraia.com.br/cilios-posticos-kiss-ny-impress-press-on-falsies-refil-02-1023740.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3474636975358</t>
+          <t>651552</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Condicionador L'Oréal Professionnel Serie Expert Vitamino Color Preserva a Cor 750ml</t>
+          <t>ESCOVA DENTAL INFANTIL JADEFROG SUPERMAN MACIA 331</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>243.9</v>
+        <v>12.82</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/l-oreal-professionnel-serie-expert-vitamino-color-condicionador-750ml-759199.html</t>
+          <t>https://www.drogaraia.com.br/escova-dental-infantil-jadefrog-superman-macia-331-651552.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7908885315376</t>
+          <t>8411061083659</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO+ CONDICIONADOR GOTA DOURADA FORTALECIMENTO QUEDA</t>
+          <t>Carolina Herrera Good Girl Blush Elixir Edp - Feminino 80ml</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>44.9</v>
+        <v>1019</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-shampoo-condicionador-gota-dourada-fortalecimento-queda-1018862.html</t>
+          <t>https://www.drogaraia.com.br/carolina-herrera-good-girl-blush-elixir-edp-feminino-80ml-975761.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8011003809219</t>
+          <t>7792252453040</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Eros Versace Eau de Toilette 100ml - Perfume Masculino</t>
+          <t>KIT CADIVEU PROFESSIONAL 6 VOLUMES - OXIDANTE 900ML (2 UNIDADES)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>511.9</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-versace-eros-edt-masculino-100ml-946837.html</t>
+          <t>https://www.drogaraia.com.br/kit-cadiveu-professional-6-volumes-oxidante-900ml-2-unidades-899642.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>824179</t>
+          <t>8011003864089</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KIT SABONETE VEGETAL HERBISSIMO MENTOS C/5 UNIDADES 1 CADA FRAGRâNCIA</t>
+          <t>Toy 2 Bubble Gum Moschino Eau de Toilette 100ml - Perfume Feminino</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>27.9</v>
+        <v>519.95</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-sabonete-vegetal-herbissimo-mentos-c-5-unidades-1-cada-fragrancia-824179.html</t>
+          <t>https://www.drogaraia.com.br/perfume-moschino-toy-2-bubble-gum-feminino-100ml-955803.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7898130554431</t>
+          <t>7899706239240</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MáSCARA PARA CíLIOS INCOLOR EXTEND LASHES VIVAI</t>
+          <t>ESMALTE COLORAMA FINI DE MILHõES</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>23.47</v>
+        <v>21.99</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/mascara-para-cilios-incolor-extend-lashes-vivai-869777.html</t>
+          <t>https://www.drogaraia.com.br/esmalte-colorama-fini-de-milhoes-1014318.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7898589682716</t>
+          <t>7891024028841</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Girl Star Parfum Brasil Eau de Toilette 15ml - Perfume Feminino</t>
+          <t>Enxaguante Bucal Colgate Total 12 Clean Mint 1L</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>49.99</v>
+        <v>42.9</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-feminino-deo-colonia-parfum-absoluty-girl-star-15ml-903564.html</t>
+          <t>https://www.drogaraia.com.br/enxaguante-bucal-colgate-total-12-clean-mint-1l-664939.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7898902624409</t>
+          <t>8058664136087</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TIROCEPT GEL - RECEPTQUâNTIC - FLORAL PARA INSEGURANçA</t>
+          <t>Chupeta Chicco Physio Forma Soft 6 - 12 Meses Azul com 1 unidade</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>99</v>
+        <v>39.9</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tirocept-gel-receptquantic-floral-para-inseguranca-814445.html</t>
+          <t>https://www.drogaraia.com.br/chicco-chupeta-physio-forma-soft-6-12m-azul.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7898148290550</t>
+          <t>901764</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Captopril 50mg 30 comprimidos Farmaco Prati Genérico</t>
+          <t>Bota comfort preta curta hidrolight g</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.46</v>
+        <v>198</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/captopril-50mg-prati-generico-30-comprimidos.html</t>
+          <t>https://www.drogaraia.com.br/bota-comfort-preta-curta-hidrolight-g-901764.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7897104925468</t>
+          <t>3701129803448</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pré-Treino em Gel Body Action Nuclear Rush Frutas Vermelhas Sachê 25g 10 unidades </t>
+          <t>Protetor Solar Facial Bioderma Photoderm Nude Touch Mineral FPS 50+ Claro 40ml</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>66.79000000000001</v>
+        <v>111.99</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/nuclear-rush-gel-10-saches-25g-frutas-vermelhas-bodyaction-732256.html</t>
+          <t>https://www.drogaraia.com.br/protetor-solar-facial-photoderm-nude-touch-fps50-cor-claro.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>898184</t>
+          <t>656457</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4UNI LEITE DE COCO POUCH 200ML - COPRA</t>
+          <t>Hi whey sem sabor essential nutrition 375g</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>21.87</v>
+        <v>274.88</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/4uni-leite-de-coco-pouch-200ml-copra-898184.html</t>
+          <t>https://www.drogaraia.com.br/hi-whey-sem-sabor-essential-nutrition-375g-656457.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7891033535224</t>
+          <t>7896609542927</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EUDORA SIAGE CC CREAM 12 EM 1 RECONSTROI OS FIOS 100ML</t>
+          <t>PAYOT BOCA ROSA BEAUTY MEU GATINHO - CANETA DELINEADORA 0.24G Preto</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>52.99</v>
+        <v>43</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/eudora-siage-cc-cream-12-em-1-reconstroi-os-fios-100ml-929145.html</t>
+          <t>https://www.drogaraia.com.br/payot-boca-rosa-beauty-meu-gatinho-caneta-delineadora-0-24g-735521.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7891746041234</t>
+          <t>7896132133012</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BOTA IMOBILIZADORA BRIG-S CURTA TAM P SALVAPé</t>
+          <t>Pó COMPACTO MARCHETTI ESTRELA BEGE MéDIO 3</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>254.9</v>
+        <v>31.85</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/bota-imobilizadora-brig-s-curta-tam-p-salvape-675118.html</t>
+          <t>https://www.drogaraia.com.br/po-compacto-marchetti-estrela-bege-medio-3-989106.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7898623956711</t>
+          <t>6015045349315</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kit Salon Line Hidra Ceramidas Shampoo 300ml + Condicionador 300ml</t>
+          <t>KIT 2 OLEO DE BORRAGEM 500MG COM 60 CAPSULAS MAXINUTRI</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>23.99</v>
+        <v>118</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-shampoo-condicionador-salon-line-hidra-ceramidas.html</t>
+          <t>https://www.drogaraia.com.br/kit-2-oleo-de-borragem-500mg-com-60-capsulas-maxinutri-1009958.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>7896094211391</t>
+          <t>7791969016012</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Libiam Tibolona 2,5mg 84 comprimidos</t>
+          <t>Desodorante Antitranspirante Aerosol Nivea Fresh Natural Feminino 48h 150ml</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>201.98</v>
+        <v>17.65</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/libiam-2-5-mg-84-comprimidos.html</t>
+          <t>https://www.drogaraia.com.br/desodorante-aerosol-nivea-feminino-fresh-natural-150ml-890978.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7898352514114</t>
+          <t>7908609504192</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Shampoo Truss Blond 300ml</t>
+          <t>KIT 5 BATATA DOCE ROXA EM Pó 100% PURA 400G UNILIFE</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>141.16</v>
+        <v>143.9</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/truss-shampoo-blond-300ml-790655.html</t>
+          <t>https://www.drogaraia.com.br/kit-5-batata-doce-roxa-em-po-100-pura-400g-unilife-786341.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>980877</t>
+          <t>990674</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MULETA CANADENSE ALUMíNIO REGULáVEL 65 KG D6 DELLAMED CINZA</t>
+          <t>PRESILHA PRENDEDOR DE CABELO GISELE MODELO 1</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>68</v>
+        <v>24.9</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/muleta-canadense-aluminio-regulavel-65-kg-d6-dellamed-cinza-980877.html</t>
+          <t>https://www.drogaraia.com.br/presilha-prendedor-de-cabelo-gisele-modelo-1-990674.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7890000039376</t>
+          <t>7337390174374</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TESOURA CIRúRGICA ÍRIS OU GENGIVA ABC CURVA 12CM - UNIDADE</t>
+          <t>SUPLEMENTO ALIMENTAR ÓLEO DE FíGADO DE BACALHAU 1000MG COM 90 CáPSULAS - NOW FODDS</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>34.95</v>
+        <v>114.99</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tesoura-cirurgica-iris-ou-gengiva-abc-curva-12cm-unidade-739367.html</t>
+          <t>https://www.drogaraia.com.br/suplemento-alimentar-oleo-de-figado-de-bacalhau-1000mg-com-90-capsulas-now-fodds-822560.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3461020014021</t>
+          <t>7898670100037</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Esthederm Inten Hyaluronic Creme 50Ml</t>
+          <t>Mix Magnésio- Treonato, Dimalato e Taurato- Nutrigenes</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>416.9</v>
+        <v>49.75</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/esthederm-inten-hyaluronic-creme-50ml-682344.html</t>
+          <t>https://www.drogaraia.com.br/mix-magnesio-treonato-dimalato-e-taurato-nutrigenes-936583.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7896111985793</t>
+          <t>7898962011515</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ESMALTE IMPALA GLITTER COLEçãO VIVA AME E BRILHE BRILHE COMO DIAMANTE</t>
+          <t>GELO ARTIFICIAL TOP SEK 700G | KIT COM 20 UNIDADES</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9.09</v>
+        <v>165.88</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/esmalte-impala-glitter-colecao-viva-ame-e-brilhe-brilhe-como-diamante-643011.html</t>
+          <t>https://www.drogaraia.com.br/gelo-artificial-top-sek-700g-kit-com-20-unidades-939138.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>7898641070888</t>
+          <t>998313</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WHEY PROTEIN CONCENTRADO DUX COOKIES 900G</t>
+          <t>CADEIRA DE REFEIçãO EASY SAFETY 1ST - BLACK</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>203.92</v>
+        <v>269.9</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/whey-protein-concentrado-dux-cookies-900g-948588.html</t>
+          <t>https://www.drogaraia.com.br/cadeira-de-refeicao-easy-safety-1st-black-998313.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>918076</t>
+          <t>7898599684892</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KIT CICLO LA VIDA - DEO COLôNIA 30ML + LOçãO HIDRATANTE 240ML</t>
+          <t>Batom Líquido Matte Makiê By Marco Biaggi Paloma - 5ml</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>90</v>
+        <v>35.09</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-ciclo-la-vida-deo-colonia-30ml-locao-hidratante-240ml-nulo-918076.html</t>
+          <t>https://www.drogaraia.com.br/batom-liquido-matte-makie-by-marco-biaggi-paloma-5ml-895542.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7896658027246</t>
+          <t>7908622805542</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Profuse Puriance Sabonete Barra 80G</t>
+          <t>AGULHA DESCARPACK HIPODÉRMICA DESCARTÁVEL 25X0,80MM CX 500UN</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>96.22</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/profuse-puriance-sabonete-barra-80g-687961.html</t>
+          <t>https://www.drogaraia.com.br/agulha-descarpack-hipodermica-descartavel-25x0-80mm-cx-500un-763922.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>7898270232725</t>
+          <t>7899852024530</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MEIA COXA 7/8 ATTIVA ALTA COMPRESSAO 20-30 FEM FECHADA NATURAL ESCURO M</t>
+          <t>DELINEADOR LíQUIDO VULT CAMILA LOURES MARROM 3GR</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>107.99</v>
+        <v>38.35</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/meia-coxa-7-8-attiva-alta-compressao-20-30-fem-fechada-natural-escuro-748105.html</t>
+          <t>https://www.drogaraia.com.br/delineador-liquido-vult-camila-loures-marrom-3gr-946642.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>7896235354215</t>
+          <t>7896222718860</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Desodorante Antitranspirante Aerosol Monange Clinical Conforto Feminino 96H 150Ml</t>
+          <t>Lubrificante íntimo olla mix sensations 50g</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>20.15</v>
+        <v>29</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/desodorante-aerosol-antitranspirante-feminino-monange-clinical-conforto-150ml-643946.html</t>
+          <t>https://www.drogaraia.com.br/lubrificante-intimo-olla-mix-sensations-50g-873150.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7891033751402</t>
+          <t>3337875686471</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shampoo EuMe Crespos &amp; Cacheados 250ml</t>
+          <t>PROTETOR SOLAR ANTHELIOS HIDRAOX FPS60 SEM COR ANTI-IDADE LA ROCHE-POSAY 50G</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>13.49</v>
+        <v>133.99</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/eume-shampoo-cachos-250ml.html</t>
+          <t>https://www.drogaraia.com.br/protetor-solar-anthelios-hidraox-fps60-sem-cor-anti-idade-la-roche-posay-50g-937642.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>924590</t>
+          <t>5708932605106</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KIT 2 BIOFACTOR PRIMAVITTA FREQUENCIAIS FLORAL ÚTERO 2X50ML</t>
+          <t>BRAVA PASTA ESTOMIA COLOPLAST 12050 60G SEM ÁLCOOL - UNIDADE</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>143</v>
+        <v>134.82</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-2-biofactor-primavitta-frequenciais-floral-utero-2x50ml-924590.html</t>
+          <t>https://www.drogaraia.com.br/brava-pasta-estomia-coloplast-12050-60g-sem-alcool-unidade-719498.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7898664810010</t>
+          <t>3145891165203</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>COMPRE 2 LEVE 3 POTES CáLCIO DE OSTRAS 800MG 60 CáPSULAS</t>
+          <t>CHANEL COCO MADEMOISELLE FEMININO EAU DE PARFUM 100ML</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>181.3</v>
+        <v>1381.08</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/compre-2-leve-3-potes-calcio-de-ostras-800mg-60-capsulas-707167.html</t>
+          <t>https://www.drogaraia.com.br/chanel-coco-mademoiselle-feminino-eau-de-parfum-100ml-694236.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7899852024950</t>
+          <t>7898952570121</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Batom Aquatint Vult Gel Violet 5.5ml</t>
+          <t>COLCHãO SEM MOTOR AIR PLUS 130 CéLULAS DELLAMED Bege</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>20.15</v>
+        <v>149</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/batom-aquatint-vult-gel-violet-5-5ml-949486.html</t>
+          <t>https://www.drogaraia.com.br/colchao-sem-motor-air-plus-130-celulas-dellamed-697376.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7897517931360</t>
+          <t>7898944775022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pincel de Tintura Vertix Médio - 6 unidades</t>
+          <t>ÔMEGA 3 (90 CAPS) - PADRãO: ÚNICO</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>19.77</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/vertix-pincel-de-tintura-medio-com-6-unidade.html</t>
+          <t>https://www.drogaraia.com.br/omega-3-90-caps-padrao-unico-987378.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7908038604586</t>
+          <t>3386460028356</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FOREVER LISS BLINDAGEM CAPILAR CONDICIONADOR 200G</t>
+          <t>Presence Dune Montblanc Eau de Toilette 75ml - Perfume Feminino</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>23.9</v>
+        <v>719.85</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/forever-liss-blindagem-capilar-condicionador-200g-886467.html</t>
+          <t>https://www.drogaraia.com.br/mont-blanc-presence-dune-fem-75ml-828714.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7891182019378</t>
+          <t>643169698116</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WELLA PROFESSIONALS WELLASTRATE SUAVE - CREME ALISANTE 125G</t>
+          <t>Aplicador do Conjunto de Infusão Quick-Set (Quick Serter) Medtronic MMT-305QS com 1 unidade</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>54.9</v>
+        <v>135</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/wella-professionals-wellastrate-suave-creme-alisante-125g-905244.html</t>
+          <t>https://www.drogaraia.com.br/medtronic-aplicador-do-conjunto-de-infusao-quick-set-quick-serter-mmt-305qs.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>725008</t>
+          <t>1022618</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KIT 3 REFIL SABONETE LíQUIDO PROTEX LIMPEZA PROFUNDA 900ML</t>
+          <t>TERMôMETRO PARA ÁGUA GIRAFINHA AMARELO E LARANJA - BUBA</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>104.7</v>
+        <v>25.9</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-3-refil-sabonete-liquido-protex-limpeza-profunda-900ml-725008.html</t>
+          <t>https://www.drogaraia.com.br/termometro-para-agua-girafinha-amarelo-e-laranja-buba-1022618.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7908458309047</t>
+          <t>7891142203762</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KIT DUPLINHA SOS HIDRATAçãO ULTRA CACHOS E CREME PARA PENTEAR DEFINIçãO MáXIMA 1KG SALON LINE</t>
+          <t>MANTECORP GLYCARE SéRUM FR 30ML</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>241.12</v>
+        <v>561.77</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-duplinha-sos-hidratacao-ultra-cachos-e-creme-para-pentear-definicao-maxima-1kg-salon-line-863168.html</t>
+          <t>https://www.drogaraia.com.br/mantecorp-glycare-serum-fr-30ml-790877.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>987655</t>
+          <t>7896004729459</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KIT 2X WHEY PROTEIN ISO - X  PROTEIN COMPLEX 900G - XPRO NUTRITION Bananachocolate</t>
+          <t>Atorvastatina Cálcica 80mg 30 comprimidos EMS Genérico</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>399.99</v>
+        <v>241.59</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-2x-whey-protein-iso-x-protein-complex-900g-xpro-nutrition-bananachocolate-987655.html</t>
+          <t>https://www.drogaraia.com.br/atorvastatina-calcica-80mg-ems-genericos-30-comprimidos-revestidos.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7898956640196</t>
+          <t>745110315032</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kit Desodorante Antitranspirante Creme Herbíssimo Action 48h Sem Álcool 55g 12 unidades</t>
+          <t>BCAA 2400 60 CáPS - XPRO NUTRITION</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>97.90000000000001</v>
+        <v>59.99</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-12-desodorante-creme-herbissimo-action-antitranspirante-55g-963974.html</t>
+          <t>https://www.drogaraia.com.br/bcaa-2400-60-caps-xpro-nutrition-685447.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7896206402976</t>
+          <t>892070</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nexium Esomeprazol Magnésico 40mg 28 comprimidos</t>
+          <t>EUDORA SIàGE CONDICIONADOR CAUTERIZAçãO DOS FIOS 200ML</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>382.97</v>
+        <v>49.8</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/nexium-40-mg-28-comprimidos-revestidos.html</t>
+          <t>https://www.drogaraia.com.br/eudora-siage-condicionador-cauterizacao-dos-fios-200ml-892070.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7896311707973</t>
+          <t>7896852615294</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Suplemento Integralmédica Therma Pro Hardcore 60 cápsulas</t>
+          <t>Tonalizante Superia Color 670 Chocolate</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>59.9</v>
+        <v>37.38</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/therma-pro-hardcore-60-caps-padrao-unico-882742.html</t>
+          <t>https://www.drogaraia.com.br/tonalizante-superia-color-670-chocolate-722772.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7896094907119</t>
+          <t>887242</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Maracugina 420mg 20 Comprimidos Revestidos</t>
+          <t>Bigens Kit 2X Própolis Verde Alecrim 60 Cápsulas, Vit C, D3, Zinco</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>38.88</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/maracugina-450mg-com-20-comprimidos-revestidos.html</t>
+          <t>https://www.drogaraia.com.br/biogens-kit-2x-propolis-verde-alecrim-60cps-vit-c-d3-zinco-887242.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8022297071411</t>
+          <t>652418100331</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Alfaparf Style Stories Defining Wax - Cera Suave 75Ml</t>
+          <t>N.p.p.e sh-rd sage purifying semi-treatment low poo condicionador 200ml</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>119.9</v>
+        <v>159.9</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/alfaparf-style-stories-defining-wax-cera-suave-75ml-771355.html</t>
+          <t>https://www.drogaraia.com.br/n-p-p-e-sh-rd-sage-purifying-semi-treatment-low-poo-condicionador-200ml-723853.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7899760800455</t>
+          <t>7793632600139</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>L´ARRËE COLOR COLORAçãO PERMANENTE 5.0 CASTANHO CLARO - 60G</t>
+          <t>KIT MY PLEASURE + SéRUM ÍNTIMO + VELA DE MASSAGEM DE VERBENA BY LAURA MULLER - INTT</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>27.77</v>
+        <v>276.9</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/l-039arree-color-colorac-o-permanente-5-0-castanho-claro-60g-971722.html</t>
+          <t>https://www.drogaraia.com.br/kit-my-pleasure-serum-intimo-vela-de-massagem-de-verbena-by-laura-muller-intt-911815.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7898708732278</t>
+          <t>7891317009755</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WHEY 100% HD POTE (900G) - SABOR: CHOCOLATE</t>
+          <t>Tamisa 30 Gestodeno 75mcg + Etinilestradiol 30mcg 84 comprimidos</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>149.9</v>
+        <v>112.99</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/whey-100-hd-pote-900g-sabor-chocolate-883147.html</t>
+          <t>https://www.drogaraia.com.br/tamisa-30-sem-parar-com-84-comprimidos.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7896311763849</t>
+          <t>8433982002243</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Glutamina Glutamine Nutrify Neutro 500g</t>
+          <t>United Dreams Aim High Benetton Eau De Toilette - Perfume Masculino 100ml</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>121.91</v>
+        <v>229</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/glutamine-770516.html</t>
+          <t>https://www.drogaraia.com.br/benetton-aim-high-masc-100ml-704349.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>7898626442587</t>
+          <t>726240</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Proteína Isolada em Pó Profit Laboratórios Isolate Protein Mix Banana com Canela 907g</t>
+          <t>BATATA DOCE ROXA CHIPS ROOTS TO GO 45G</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>189.92</v>
+        <v>20.29</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/isolate-protein-mix-907g-banana-com-canela-profit-763545.html</t>
+          <t>https://www.drogaraia.com.br/batata-doce-roxa-chips-roots-to-go-45g-726240.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7896094208933</t>
+          <t>7908885324842</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vatis Cloridrato Propafenona 150mg 60 comprimidos</t>
+          <t>AGUA OXIGENADA YAMA 100ML 30 VOLUMES - KIT C/ 12UN</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>92.98999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/vatis-150-mg-60-comprimidos-revestidos.html</t>
+          <t>https://www.drogaraia.com.br/agua-oxigenada-yama-100ml-30-volumes-kit-c-12un-1023805.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7500435184922</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Creme de Tratamento Aussie 3 Minutos Milagrosos Cachos e Crespos 236ml</t>
+          <t>Kit Truss Frizz Zero Disciplinante Mask (4 Produtos)</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>59.9</v>
+        <v>599.9</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/aussie-3-minutos-milagrosos-cachos-e-crespos-236ml.html</t>
+          <t>https://www.drogaraia.com.br/kit-truss-frizz-zero-disciplinante-mask-4-produtos-774690.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>7896013563839</t>
+          <t>7899706186179</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TINTURA MAXTON COR: 8.26 MARSALA</t>
+          <t>PROTETOR SOLAR FACIAL COM COR 2.0 LA ROCHE-POSAY ANTHELIOS ULTRA COVER FPS60 30G</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>26.9</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tintura-maxton-cor-8-26-marsala-935284.html</t>
+          <t>https://www.drogaraia.com.br/protetor-solar-facial-com-cor-2-0-la-roche-posay-anthelios-ultra-cover-fps60-30g-819893.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7896098809747</t>
+          <t>7891106007030</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Copo De Treinamento 360° Evolution Magic Cup Rosa Gata Nuk</t>
+          <t>Xarelto Rivaroxabana 10mg 10 Comprimidos</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>69.90000000000001</v>
+        <v>97.78</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/copo-de-treinamento-360-evolution-magic-cup-rosa-gata-nuk-715347.html</t>
+          <t>https://www.drogaraia.com.br/xarelto-10mg-10-comprimidos-revestidos.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7898919865857</t>
+          <t>7909463683665</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Fosvita Vitafor Fibras Alimentares 250g</t>
+          <t>Kit 2x: leite vegetal barista a tal da castanha 1l</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>77.90000000000001</v>
+        <v>55.88</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/fosvita-regulador-intestinal-vitafor-250g-696774.html</t>
+          <t>https://www.drogaraia.com.br/kit-2x-leite-vegetal-barista-a-tal-da-castanha-1l-833401.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7500435148436</t>
+          <t>7897975696986</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lenço Umedecido Pampers Aroma de Lavanda 48 unidades </t>
+          <t>Protetor Solar Facial Adcos Aqua Fluid FPS 50 50ml</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>17.9</v>
+        <v>111.75</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/pampers-lencos-umedecidos-aroma-de-lavanda-48-unidades.html</t>
+          <t>https://www.drogaraia.com.br/adcos-protetor-solar-aqua-fluid-fps50-50ml.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>667555168632</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Wella Professionals Oil Reflections - Shampoo 1L +Máscara Capilar 500ml+Oil Reflections Ligth 30ml</t>
+          <t>VICTORIA´S SECRET BLISSFUL GARDEN - BODY LOTION 236ML</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>489.99</v>
+        <v>155</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/wella-professionals-oil-reflections-shampoo-1l-mascara-capilar-500ml-oil-reflections-ligth-30ml-773876.html</t>
+          <t>https://www.drogaraia.com.br/victoria-039s-secret-blissful-garden-body-lotion-236ml-876146.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>7793537678240</t>
+          <t>7891010503024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TRATAMENTO PARA ESPINHAS E CELULITE NO BUMBUM KIT INOVADOR</t>
+          <t>Absorvente Externo Sempre Livre Adapt Cobertura Suave Com Abas 8 Unidades</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>46.7</v>
+        <v>6.9</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/tratamento-para-espinhas-e-celulite-no-bumbum-kit-inovador-918434.html</t>
+          <t>https://www.drogaraia.com.br/absorvente-externo-sempre-livre-adapt-cobertura-suave-com-abas-8-unidades-666547.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7898687730678</t>
+          <t>7908622800646</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SUPLEMENTO CARTLIV ULTRA MDK 60 CáPSULAS - EQUALIV</t>
+          <t>FITA ADESIVA EM GEL SILICONE PARA CICATRIZ 70CMX3CM KELOGEL</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>90</v>
+        <v>138.9</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/suplemento-cartliv-ultra-mdk-60-capsulas-equaliv-778818.html</t>
+          <t>https://www.drogaraia.com.br/fita-adesiva-em-gel-silicone-para-cicatriz-70cmx3cm-kelogel-739922.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7897888806922</t>
+          <t>717226505133</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SABONETE LíQUIDO DETA GOLD LíRIO BRANCO 490ML</t>
+          <t>Condicionador John Frieda Highlight Activanting for Blondes 250ml</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>19.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/sabonete-liquido-deta-gold-lirio-branco-490ml-831862.html</t>
+          <t>https://www.drogaraia.com.br/sheer-blonde-condicionador-louro-champanhe-e-platina-250g.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7896671692919</t>
+          <t>7898692301894</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SABONETE ÍNTIMO FLORES E VEGETAIS NEUTRO 250ML</t>
+          <t>Proteína Vegetal Plant Power Protein Morango 490g</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>30.55</v>
+        <v>223.88</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/sabonete-intimo-flores-e-vegetais-neutro-250ml-1003416.html</t>
+          <t>https://www.drogaraia.com.br/proteina-vegana-morango-plant-power-protein-490g-927009.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>915225</t>
+          <t>875540</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CâMARA DE AR 24X1.3/8 POL PIRELLI  PARA CADEIRA DE RODAS</t>
+          <t>POLVILHO ANTISSéPTICO SPORT 100G - GRANADO</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>30.5</v>
+        <v>26.95</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/camara-de-ar-24x1-3-8-pol-pirelli-para-cadeira-de-rodas-915225.html</t>
+          <t>https://www.drogaraia.com.br/polvilho-antisseptico-sport-100g-granado-039-875540.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7891317011284</t>
+          <t>7898728324231</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sonic Cloridrato de Trazodona 100mg 30 comprimidos</t>
+          <t>Shampoo Abelha Rainha Óleos Nutritivos Intensive Regeneração 300ml</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>63.59</v>
+        <v>31.99</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/sonic-100mg-30-comprimidos-c1.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-oleos-nutritivos-intensive-abelha-rainha-300ml-881754.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>7898655096768</t>
+          <t>7898352514114</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MINOXIHARD® LOçãO PARA BARBA 80ML</t>
+          <t>Shampoo Truss Blond 300ml</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>99</v>
+        <v>141.16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/minoxihardr-locao-para-barba-80ml-885052.html</t>
+          <t>https://www.drogaraia.com.br/truss-shampoo-blond-300ml-685924.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7896032684959</t>
+          <t>7898902621316</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CONDICIONADOR FARMAERVAS ALGAS, MENTA E ARNICA 320ML</t>
+          <t>HALGALIS GEL - IONQUâNTIC - FLORAL PARA A TIREóIDE</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>35.9</v>
+        <v>96</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/condicionador-farmaervas-algas-menta-e-arnica-320ml-976121.html</t>
+          <t>https://www.drogaraia.com.br/halgalis-gel-ionquantic-floral-para-a-tireoide-833258.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7898656390704</t>
+          <t>6015034571581</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fralda Calça Mamypoko Super Seca XG 56 Unidades</t>
+          <t>Cosmelan 2 + hidratante calmante melan recovery - o melhor!</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>258.99</v>
+        <v>1089.9</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/fralda-calca-descartavel-mamypoko-super-seca-xg-56-unidades-971541.html</t>
+          <t>https://www.drogaraia.com.br/cosmelan-2-hidratante-calmante-melan-recovery-o-melhor-815288.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7898000177104</t>
+          <t>7897169222922</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KIT 5 MAGNéSIO MALATO PREMIUM 60 CáPSULAS DE 500MG NATALY</t>
+          <t>REFIL DE LIXA PARA PéS SANTA CLARA PRETA GROSSA 2292 C/12UN</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>178.9</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-5-magnesio-malato-premium-60-capsulas-de-500mg-nataly-sem-sabor-786029.html</t>
+          <t>https://www.drogaraia.com.br/refil-de-lixa-para-pes-santa-clara-preta-grossa-2292-c-12un-654161.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7896098814819</t>
+          <t>7500435204019</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KIT 2 CHUPETAS SPACE BOY  0 á 6 MESES AZUL  - NUK</t>
+          <t>Sabonete Íntimo e Gel para Depilação Gillette Venus Especial para Área Íntima 2 em 1 190ml</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>59.9</v>
+        <v>35.59</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-2-chupetas-space-boy-0-a-6-meses-azul-nuk-725392.html</t>
+          <t>https://www.drogaraia.com.br/venus-intima-2-em-1-sabonete-intimo-e-gel-para-depilacao-190ml.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7896094211056</t>
+          <t>7890610257252</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Reconter ODT Escitalopram Base 20mg 30 comprimidos</t>
+          <t>PALMILHA ANATôMICA TRATAMENTO IMEDIATO ESPORãO CALCâNEO ORIGINAL</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>157.98</v>
+        <v>39.9</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/reconter-odt-20mg-30-comprimidos-c1.html</t>
+          <t>https://www.drogaraia.com.br/palmilha-anatomica-tratamento-imediato-esporao-calcaneo-original-983897.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7899347764231</t>
+          <t>7896852611890</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CINTA BERMUDA PARA GESTANTE BEGE</t>
+          <t>COLORAçãO COLOR INTENSY AMEND COR:1.0 PRETO</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>459.9</v>
+        <v>58.83</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/cinta-bermuda-para-gestante-bege-763657.html</t>
+          <t>https://www.drogaraia.com.br/coloracao-color-intensy-amend-cor-1-0-preto-880036.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>980931</t>
+          <t>7898728320530</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PERFUME CAROLINA HERRERA CH MEN - EAU DE TOILETTE - 100 ML</t>
+          <t>Batom Brilho Intenso Marrom Desejo Fps 15 Shine Colors Abelha Rainha 3,7g</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>768.48</v>
+        <v>19.99</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/perfume-carolina-herrera-ch-men-eau-de-toilette-100-ml-980931.html</t>
+          <t>https://www.drogaraia.com.br/batom-brilho-intenso-marrom-desejo-fps-15-shine-colors-abelha-rainha-3-7g-971415.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7897975698911</t>
+          <t>7891150070301</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Sérum Concentrado Clareador Adcos Melan-Off B3 30g</t>
+          <t>Shampoo seda recarga natural bambu + biotina 325ml</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>319</v>
+        <v>14.35</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/adcos-melan-off-serum-concentrado-clareador-30g.html</t>
+          <t>https://www.drogaraia.com.br/shampoo-seda-recarga-natural-bambu-biotina-325ml-890672.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7898000126188</t>
+          <t>7897930750043</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KIT COM 02 - CáLCIO MDK (CáLCIO, MAGNéSIO, VITAMINA D E K2) 60 CAPSULAS TUTTIFLORA</t>
+          <t>GALDERMA SOAPEX SABONETE 80G</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>78.90000000000001</v>
+        <v>56.95</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-com-02-calcio-mdk-calcio-magnesio-vitamina-d-e-k2-60-capsulas-tuttiflora-933359.html</t>
+          <t>https://www.drogaraia.com.br/galderma-soapex-sabonete-80g-738668.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1009898769333</t>
+          <t>7898902620777</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kit L'Oréal Professionnel Serie Expert Blondifier Gloss - Shampoo E Condicionador E Máscara</t>
+          <t>NEFRON - BIOFACTOR - FLORAL PARA A BEXIGA NúCLEO QUâNTICO</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>438.9</v>
+        <v>78</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-l-oreal-professionnel-serie-expert-blondifier-gloss-shampoo-e-condicionador-e-mascara-687889.html</t>
+          <t>https://www.drogaraia.com.br/nefron-biofactor-floral-para-a-bexiga-nucleo-quantico-814358.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7805089945784</t>
+          <t>7896004736884</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Combo Siàge Hidratação Micelar: Shampoo 250Ml + Condicionador 200Ml + Leave-In 100Ml</t>
+          <t>Lipistatina Sinvastatina 40mg 30 comprimidos</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>142.97</v>
+        <v>57.99</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/combo-siage-hidratacao-micelar-shampoo-250ml-condicionador-200ml-leave-in-100ml-635450.html</t>
+          <t>https://www.drogaraia.com.br/lipistatina-40mg-2-blister-15-comprimidos-revestidos.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>842147</t>
+          <t>4005808956487</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SUPORTE PARA OMBRO - HIDROLIGHT P</t>
+          <t>PROTETOR SOLAR NIVEA SUN FPS 30 PROTETOR E BRONZE 200ML</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>102.9</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/suporte-para-ombro-hidrolight-p-842147.html</t>
+          <t>https://www.drogaraia.com.br/protetor-solar-nivea-sun-fps-30-protetor-e-bronze-200ml-831909.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7797941936569</t>
+          <t>7895389148138</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KIT LOKENZZI ONDAS MARCANTES SPRAY DAY AFTER + MáSCARA 250G</t>
+          <t>Hidratante Facial Gel Creme Oil Free Dermage Secatriz Prebio Control 40G</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>112.8</v>
+        <v>129.99</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/kit-lokenzzi-ondas-marcantes-spray-day-after-mascara-250g-1015040.html</t>
+          <t>https://www.drogaraia.com.br/hidratante-facial-gel-creme-oil-free-dermage-secatriz-prebio-control-40g-692257.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7908329703981</t>
+          <t>7898258951761</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JACQUES JANINE PROFESSIONNEL REPAIR - CONDICIONADOR 750ML</t>
+          <t>MEL ORGâNICO VIDRO 500GR - BALDONI</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>40.99</v>
+        <v>40.51</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/jacques-janine-professionnel-repair-condicionador-750ml-918272.html</t>
+          <t>https://www.drogaraia.com.br/mel-organico-vidro-500gr-baldoni-921606.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3474636940455</t>
+          <t>7898966596117</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REDKEN EXTREME BLEACH RECOVERY SHAMPOO 300ML</t>
+          <t>Espuma de Higiene Íntima Nuaá Suave Calm 150ml</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>114.9</v>
+        <v>41.9</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/redken-extreme-bleach-recovery-shampoo-300ml-886327.html</t>
+          <t>https://www.drogaraia.com.br/nuaa-espuma-de-higiene-intima-suave-calm-150ml.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>602883980754</t>
+          <t>7897517924270</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>QUALY VITAM OLHOS C/60 CáPSULAS - QUALYNUTRI</t>
+          <t>Escova de Cabelo Ricca Almofadada Pink - 1 unidade</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>59.99</v>
+        <v>13.68</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/qualy-vitam-olhos-c-60-capsulas-qualynutri-939440.html</t>
+          <t>https://www.drogaraia.com.br/ricca-escova-pink-oval-almofadada-1-unidade.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>841106</t>
+          <t>848975</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Banderas King Of Seduction Absolute Eau De Toilette - Perfume Masculino 200Ml</t>
+          <t>CARBOLIFT (900G) ESSENTIAL NUTRITION</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>338</v>
+        <v>264.6</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/banderas-king-of-seduction-absolute-eau-de-toilette-perfume-masculino-200ml-982116.html</t>
+          <t>https://www.drogaraia.com.br/carbolift-900g-essential-nutrition-848975.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3474637106393</t>
+          <t>7896094931220</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>L'Oréal Professionnel Serie Expert Serioxyl Advanced - Shampoo Densificante 300ml</t>
+          <t>Polivitamínico Addera Muscular 60 comprimidos</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>139.9</v>
+        <v>249.9</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://www.drogaraia.com.br/l-oreal-professionnel-serie-expert-serioxyl-advanced-shampoo-300ml-748742.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>744956</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Meia 3/4 Alta Compressão 20-30mmHg Aberta Bege G3 Basic</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>175.13</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/meia-3-4-basic-972-20-30-mmhg-sigvaris-aberta-744956.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>1000552</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Sabonete Líquido Suave Alecrim Dourado - 250 Ml</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/sabonete-liquido-suave-alecrim-dourado-250-ml-1000552.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>7899838835624</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>PROTETOR ALCOCHOADO AUTOMOTIVO PARA CARRINHOS E CADEIRINHAS DE BEBê - BB356</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/protetor-alcochoado-automotivo-para-carrinhos-e-cadeirinhas-de-bebe-bb356-818118.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>7896902200616</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>REMOVEDOR DE ESMALTE FARMAX SEM ACETONA ARGAN 500ML</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/removedor-de-esmalte-farmax-sem-acetona-argan-500ml-1014691.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>7908609527917</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>KIT 2 COLAGENTEK BEAUTY VITAFOR 30 SACHêS 3,5G ABACAXI COM HORTELã</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>233.9</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-2-colagentek-beauty-vitafor-30-saches-3-5g-abacaxi-com-hortela-697646.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>679919</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Whey Protein Vitafor Whey Fort 3W Baunilha 900g</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>223.9</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/whey-fort-3w-vitafor-baunilha-900g-679919.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2000000000022</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>KIT DEPILSAM 02 KIT DANA 02</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-depilsam-02-kit-dana-02-684218.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>6018126407317</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>FINALIZADOR BIO EXTRATUS JABORANDI ANTIQUEDA 150G</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/finalizador-bio-extratus-jaborandi-antiqueda-150g-965840.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>7896609548752</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Gel secativo acnederm payot 15g</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/gel-secativo-acnederm-payot-15g-890367.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>7897517919467</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Pincel ricca rose gold duo fiber ref: 1946</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/pincel-ricca-rose-gold-duo-fiber-ref-1946-859795.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>4005808513550</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Sabonete Líquido Nivea Creme Soft 250ml</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/nivea-sabonete-liquido-creme-soft-250ml.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>914363</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Shampoo Siàge Reconstrói os Fios 400ml</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/shampoo-siage-reconstroi-os-fios-400ml-914363.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>7891262860166</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>ESCOVA DENTAL ELéTRICA INFANTIL PRINCESAS 3+ ANOS - ORAL-B</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>119</v>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/escova-dental-eletrica-infantil-princesas-3-anos-oral-b-927252.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>7702331335204</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>BERçO CERCADO PORTáTIL PARA BEBê INFINITY PREMIUM BABY Cinza</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>549.9</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/berco-cercado-portatil-para-bebe-infinity-premium-baby-cinza-964794.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>6018132981426</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SUPLEMENTO ALIMENTAR EM COMPRIMIDOS BIO EXTRATUS-60 UNIDADES</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/suplemento-alimentar-em-comprimidos-bio-extratus-60-unidades-975014.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>7908885329328</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>CREME PARA PENTEAR ACQUA KIDS 250ML MARSHMALLOW - KIT C/ 2UN</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/creme-para-pentear-acqua-kids-250ml-marshmallow-kit-c-2un-1024012.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>4618</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SPIRULINA 600MG TRUE SOURCE 120 TABLETS</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/spirulina-600mg-true-source-120-tablets-949928.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>911431</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SUPER OMEGA 3 TG 500MG - 240 CAPSULAS - ESSENTIAL NUTRITION</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>250.2</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/super-omega-3-tg-500mg-240-capsulas-essential-nutrition-911431.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>7891033930678</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>LA PIEL CRISTAIS DO HIMALAIA DES HIDRA CORPORAL 400ML</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/la-piel-cristais-do-himalaia-des-hidra-corporal-400ml-1011069.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>7898681120239</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Condicionador Lokenzzi Total Defense 320ml</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/lokenzzi-total-defense-condicionador-320ml-cabelos-livres-de-quedas-ressecamento-e-frizz-923899.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>7807157292790</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>KIT COM 10 UNIDADES ALICATE MUNDIAL PROFISSIONAL 777</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>647.6900000000001</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-com-10-unidades-alicate-mundial-profissional-777-971464.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>7896502943739</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>CADEIRA PARA AUTO BURIGOTTO PROTEGE FIX 15 A 36 KG CARAMELO U</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>501.9</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/cadeira-para-auto-burigotto-protege-fix-15-a-36-kg-caramelo-u-978212.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>7899774300408</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>AXIGRAM SOLST PROTETOR SOLAR HIDRATANTE FPS 50 TOQUE SECO 55G</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>168.87</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/axigram-solst-protetor-solar-hidratante-fps-50-toque-seco-55g-791235.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>7897517920685</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>ESCOVA DENTAL KESS PRO 10K WHITE EXTRA MACIA 2068</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>21.45</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/escova-dental-kess-pro-10k-white-extra-macia-2068-651840.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>828273</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Respiron Volumétrico Adulto</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>149.56</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/respiron-volumetrico-adulto-828273.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>7896609546734</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>BLUSH RETINOL COR TERRACOTA PAYOT 6G</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/blush-retinol-cor-terracota-payot-6g-1016237.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>7506306214972</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Desodorante Antitranspirante Aerosol Rexona Men Clinical Clean 96h 150ml</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/antitranspirante-aerosol-rexona-men-clinical-clean-150ml-895580.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>789415290564</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>KIT FACIAL NEUTROGENA HIALURôNICO HYDRO BOOST GEL + SéRUM</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>169.99</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-facial-neutrogena-hialuronico-hydro-boost-gel-serum-923679.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>859089</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>BEST WHEY BAR (49G) PEANUT BUTTER ATLHETICA NUTRITION</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>10</v>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/best-whey-bar-49g-peanut-butter-atlhetica-nutrition-859089.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>7897930777705</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Loção de Limpeza Facial Cetaphil Pele Seca e Sensível com 120ml</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/cetaphil-locao-limpeza-de-pele-120-ml.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>7908825774461</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>DESODORANTE ROLLON NIVEA 50 ML FEMININO DRY CONFORT - KIT3UN</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/desodorante-rollon-nivea-50-ml-feminino-dry-confort-kit3un-1004334.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>9000250280093</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Kit Truss Curly Duplo - Shampoo 300ml + Condicionador 300ml</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>298</v>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-truss-curly-duplo-shampoo-300ml-condicionador-300ml-923162.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>865106</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>KIT LOWELL PRO BIOPLASTIA CLINIC SHAMPOO MáSCARA E PROTEíNA (3 PRODUTOS)</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>774.99</v>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/kit-lowell-pro-bioplastia-clinic-shampoo-mascara-e-proteina-3-produtos-865106.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>1022157</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>EUDORA INSTANCE AMEIXA E PRATINÉ DES HIDRATANTE CORPO 400ML</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/eudora-instance-ameixa-e-pratine-des-hidratante-corpo-400ml-1022157.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>7891010249878</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Gel Creme Neutrogena Bright Boost Fps30 40g</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>101.99</v>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/gel-creme-neutrogena-bright-boost-fps30-40g-634616.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>7891746428462</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>TALA P/PUNHO ANTEBRAçO SALVAPE LONGA DIREITO EGG - UNIDADE</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>154.05</v>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>https://www.drogaraia.com.br/tala-p-punho-antebraco-salvape-longa-direito-egg-unidade-760512.html</t>
+          <t>https://www.drogaraia.com.br/addera-muscular-vitamina-d-2000ui-60-comprimidos.html</t>
         </is>
       </c>
     </row>
